--- a/presentation/PyramidModelRules.xlsx
+++ b/presentation/PyramidModelRules.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://docs.philips.com/personal/r_hendriks_philips_com/Documents/SW Projects/QSeaBattle/Specification/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://docs.philips.com/personal/r_hendriks_philips_com/Documents/SW Projects/QSeaBattle/presentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="251" documentId="8_{20096A4A-BA9D-483F-A080-94665FEE1233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC154D11-2DFA-4BC3-8ADE-307DF411EBFC}"/>
+  <xr:revisionPtr revIDLastSave="374" documentId="8_{20096A4A-BA9D-483F-A080-94665FEE1233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0AAD95A-8EB7-4AF5-96E6-634B2BAB8C58}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Field8,eq=0" sheetId="4" r:id="rId1"/>
-    <sheet name="Field8,eq=1" sheetId="1" r:id="rId2"/>
-    <sheet name="Field16,eq=0" sheetId="5" r:id="rId3"/>
-    <sheet name="Field16,eq=1" sheetId="2" r:id="rId4"/>
-    <sheet name="Fiel48,eq=0" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet name="Field2,eq=0" sheetId="7" r:id="rId1"/>
+    <sheet name="Field8,eq=0" sheetId="4" r:id="rId2"/>
+    <sheet name="Field8,eq=1" sheetId="1" r:id="rId3"/>
+    <sheet name="Field16,eq=0" sheetId="5" r:id="rId4"/>
+    <sheet name="Field16,eq=1" sheetId="2" r:id="rId5"/>
+    <sheet name="Fiel48,eq=0" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="39">
   <si>
     <t>Field</t>
   </si>
@@ -105,11 +106,65 @@
   <si>
     <t>"1 if (0,1) else 0"</t>
   </si>
+  <si>
+    <t>Pyramid accuracy</t>
+  </si>
+  <si>
+    <t>Phigh</t>
+  </si>
+  <si>
+    <t>Majority accururacy</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>zero flips</t>
+  </si>
+  <si>
+    <t>4 flips</t>
+  </si>
+  <si>
+    <t>2 flips</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Majority</t>
+  </si>
+  <si>
+    <t>Total in 3</t>
+  </si>
+  <si>
+    <t>Total in 2</t>
+  </si>
+  <si>
+    <t>Full pyramid</t>
+  </si>
+  <si>
+    <t>Field size 16</t>
+  </si>
+  <si>
+    <t>Full majority</t>
+  </si>
+  <si>
+    <t>3 majority +1 pyramid</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2 majority + 2 pyramid</t>
+  </si>
+  <si>
+    <t>1  majority +3 pyramid</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -262,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -277,9 +332,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,12 +807,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416556D7-58A6-4D7F-ACA7-4D6F236A6CDA}">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AD33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33FB5D7-18BF-4446-AB69-664C396954D7}">
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="12" max="12" width="8.88671875" style="13"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="13" customWidth="1"/>
     <col min="25" max="30" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
@@ -769,64 +827,34 @@
         <f ca="1">+ROUND(RAND(),0)</f>
         <v>0</v>
       </c>
-      <c r="E2" s="6">
-        <f t="shared" ref="E2:K2" ca="1" si="0">+ROUND(RAND(),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H2" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I2" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J2" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K2" s="7">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M2" s="15" t="s">
+      <c r="E2" s="7">
+        <f t="shared" ref="E2" ca="1" si="0">+ROUND(RAND(),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="M2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
-      <c r="Q2" s="15">
-        <v>0</v>
-      </c>
-      <c r="R2" s="15">
-        <v>1</v>
-      </c>
-      <c r="S2" s="15">
-        <v>2</v>
-      </c>
-      <c r="T2" s="15">
-        <v>3</v>
-      </c>
-      <c r="U2" s="15">
-        <v>4</v>
-      </c>
-      <c r="V2" s="15">
-        <v>5</v>
-      </c>
-      <c r="W2" s="15">
-        <v>6</v>
-      </c>
-      <c r="X2" s="15">
-        <v>7</v>
-      </c>
+      <c r="Q2" s="14">
+        <v>0</v>
+      </c>
+      <c r="R2" s="14">
+        <v>1</v>
+      </c>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
@@ -835,8 +863,8 @@
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="8">
-        <f ca="1">+RANDBETWEEN(0,7)</f>
-        <v>7</v>
+        <f ca="1">+RANDBETWEEN(0,1)</f>
+        <v>0</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
@@ -866,7 +894,7 @@
       <c r="C4" s="13"/>
       <c r="D4" s="4">
         <f ca="1">+OFFSET(D2,0,D3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -888,663 +916,677 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
     </row>
-    <row r="5" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-    </row>
+    <row r="5" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="14"/>
-    </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="1">
+    </row>
+    <row r="7" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
         <f ca="1">+D2</f>
         <v>0</v>
       </c>
-      <c r="E8" s="1">
-        <f t="shared" ref="E8:K8" ca="1" si="1">+E2</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="9">
-        <f ca="1">+D28</f>
-        <v>1</v>
-      </c>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="1">
+      <c r="E9" s="1">
+        <f ca="1">+E2</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="9">
+        <f ca="1">+D17</f>
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1">
         <f ca="1">+IF(Q2=$D3,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <f t="shared" ref="R8:X8" ca="1" si="2">+IF(R2=$D3,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T8" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U8" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V8" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X8" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="1">
-        <f ca="1">+MOD(D8+E8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <f ca="1">+MOD(F8+G8,2)</f>
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <f ca="1">+MOD(H8+I8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
-        <f ca="1">+MOD(J8+K8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1">
+        <f ca="1">+IF(R2=$D3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <f ca="1">+MOD(D9+E9,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="14"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="1">
-        <f ca="1">+IF(AND(NOT(Q8),R8),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <f ca="1">+IF(AND(NOT(S8),T8),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <f ca="1">+IF(AND(NOT(U8),V8),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <f ca="1">+IF(AND(NOT(W8),X8),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="U10" s="13" t="s">
+      <c r="M11" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1">
+        <f ca="1">+IF(AND(NOT(Q9),R9),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-    </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13" t="s">
+    </row>
+    <row r="12" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="3">
+      <c r="D13" s="3">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <f t="shared" ref="E12:G12" ca="1" si="3">+ROUND(RAND(),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G12" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="14"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="3">
-        <f ca="1">+IF(AND(Q10=1,D10=1),MOD(1+D12,2),D12)</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <f ca="1">+IF(AND(R10=1,E10=1),MOD(1+E12,2),E12)</f>
-        <v>0</v>
-      </c>
-      <c r="S12" s="3">
-        <f ca="1">+IF(AND(S10=1,F10=1),MOD(1+F12,2),F12)</f>
-        <v>1</v>
-      </c>
-      <c r="T12" s="3">
-        <f ca="1">+IF(AND(T10=1,G10=1),MOD(1+G12,2),G12)</f>
-        <v>1</v>
-      </c>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="13"/>
-    </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13" t="s">
+      <c r="Q13" s="3">
+        <f ca="1">+IF(AND(Q11=1,D11=1),MOD(1+D13,2),D13)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="1">
-        <f ca="1">+MOD(D12+D8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <f ca="1">+MOD(E12+F8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <f ca="1">+MOD(F12+H8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <f ca="1">+MOD(G12+J8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="13" t="s">
+      <c r="D15" s="1">
+        <f ca="1">+MOD(D13+D9,2)</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14" t="s">
+      <c r="M15" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="14"/>
-      <c r="O14" s="1">
-        <f ca="1">+MOD(O8+SUMPRODUCT(Q12:T12,Q14:T14),2)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="1">
-        <f ca="1">+MOD(Q8+R8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <f ca="1">+MOD(S8+T8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <f ca="1">+MOD(U8+V8,2)</f>
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <f ca="1">+MOD(W8+X8,2)</f>
-        <v>1</v>
-      </c>
-      <c r="U14" s="13" t="s">
+      <c r="O15" s="1">
+        <f ca="1">+MOD(O9+SUMPRODUCT(Q13:T13,Q15:T15),2)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <f ca="1">+MOD(Q9+R9,2)</f>
+        <v>1</v>
+      </c>
+      <c r="R15" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="13"/>
-    </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="1">
-        <f ca="1">+MOD(D14+E14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
-        <f ca="1">+MOD(F14+G14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" s="14"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="1">
-        <f ca="1">+IF(AND(NOT(Q14),R14),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <f ca="1">+IF(AND(NOT(S14),T14),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="S16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="13"/>
-      <c r="X16" s="13"/>
-    </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13" t="s">
+    </row>
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="2:25" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2">
+        <f ca="1">+D15</f>
+        <v>1</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="O17" s="4">
+        <f ca="1">+O15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="2:25" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12" t="b">
+        <f ca="1">+O15=SUMPRODUCT(D9:E9,Q9:R9)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:25" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:25" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26">
+        <f>0.5*1+0.5*0.5</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="W29" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y29"/>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" t="s">
+        <v>31</v>
+      </c>
+      <c r="P30" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y30"/>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="W31">
+        <v>16</v>
+      </c>
+      <c r="Y31" s="16">
+        <f>39203/65536</f>
+        <v>0.5981903076171875</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="E32" s="16">
+        <f>+C32*C32*C32*C32</f>
+        <v>1</v>
+      </c>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16">
+        <f>+(1-C32)*(1-C32)*(1-C32)*(1-C32)</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16">
+        <f>+C32*C32*(1-C32)*(1-C32)*6</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16">
+        <f>+I32+G32+E32</f>
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <f>+C32*C32*C32+(1-C32)*C32*C32*3</f>
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <f>+M32*$Y$34 + (1-M32)*(1-$Y$34)</f>
+        <v>0.75</v>
+      </c>
+      <c r="P32">
+        <f>+C32*C32+(1-C32)*(1-C32)</f>
+        <v>1</v>
+      </c>
+      <c r="W32">
+        <v>8</v>
+      </c>
+      <c r="Y32" s="16">
+        <f>163/256</f>
+        <v>0.63671875</v>
+      </c>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C33">
+        <v>0.9</v>
+      </c>
+      <c r="E33" s="16">
+        <f t="shared" ref="E33:E37" si="1">+C33*C33*C33*C33</f>
+        <v>0.65610000000000013</v>
+      </c>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16">
+        <f t="shared" ref="G33:G37" si="2">+(1-C33)*(1-C33)*(1-C33)*(1-C33)</f>
+        <v>9.999999999999991E-5</v>
+      </c>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16">
+        <f t="shared" ref="I33:I37" si="3">+C33*C33*(1-C33)*(1-C33)*6</f>
+        <v>4.859999999999999E-2</v>
+      </c>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16">
+        <f t="shared" ref="K33:K37" si="4">+I33+G33+E33</f>
+        <v>0.70480000000000009</v>
+      </c>
+      <c r="M33">
+        <f>+C33*C33*C33+(1-C33)*(1-C33)*C33*3</f>
+        <v>0.75600000000000012</v>
+      </c>
+      <c r="N33">
+        <f>+M33*$Y$34 + (1-M33)*(1-$Y$34)</f>
+        <v>0.628</v>
+      </c>
+      <c r="P33">
+        <f t="shared" ref="P33:P37" si="5">+C33*C33+(1-C33)*(1-C33)</f>
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="W33">
+        <v>4</v>
+      </c>
+      <c r="Y33" s="16">
+        <f>11/16</f>
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C34">
+        <v>0.8</v>
+      </c>
+      <c r="E34" s="16">
+        <f t="shared" si="1"/>
+        <v>0.40960000000000013</v>
+      </c>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16">
+        <f t="shared" si="2"/>
+        <v>1.5999999999999986E-3</v>
+      </c>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16">
+        <f t="shared" si="3"/>
+        <v>0.15359999999999996</v>
+      </c>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16">
+        <f>+I34+G34+E34</f>
+        <v>0.56480000000000008</v>
+      </c>
+      <c r="M34">
+        <f t="shared" ref="M34:M37" si="6">+C34*C34*C34+(1-C34)*(1-C34)*C34*3</f>
+        <v>0.6080000000000001</v>
+      </c>
+      <c r="N34">
+        <f t="shared" ref="N33:N37" si="7">+M34*$Y$34 + (1-M34)*(1-$Y$34)</f>
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="5"/>
+        <v>0.68000000000000016</v>
+      </c>
+      <c r="W34">
         <v>2</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="3">
-        <f ca="1">+ROUND(RAND(),0)</f>
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
-        <f t="shared" ref="E18" ca="1" si="4">+ROUND(RAND(),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14" t="s">
+      <c r="Y34" s="16">
+        <f>3/4</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C35">
+        <v>0.7</v>
+      </c>
+      <c r="E35" s="16">
+        <f t="shared" si="1"/>
+        <v>0.24009999999999992</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16">
+        <f t="shared" si="2"/>
+        <v>8.1000000000000048E-3</v>
+      </c>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16">
+        <f t="shared" si="3"/>
+        <v>0.26460000000000006</v>
+      </c>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16">
+        <f t="shared" si="4"/>
+        <v>0.51279999999999992</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="6"/>
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="7"/>
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="5"/>
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C36">
+        <v>0.6</v>
+      </c>
+      <c r="E36" s="16">
+        <f t="shared" si="1"/>
+        <v>0.12959999999999999</v>
+      </c>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16">
+        <f t="shared" si="2"/>
+        <v>2.5600000000000008E-2</v>
+      </c>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16">
+        <f t="shared" si="3"/>
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16">
+        <f t="shared" si="4"/>
+        <v>0.50080000000000002</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="6"/>
+        <v>0.504</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="7"/>
+        <v>0.502</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="5"/>
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C37">
+        <v>0.5</v>
+      </c>
+      <c r="E37" s="16">
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16">
+        <f t="shared" si="2"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="K39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="I40">
         <v>2</v>
       </c>
-      <c r="N18" s="14"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="3">
-        <f ca="1">+IF(AND(Q16=1,D16=1),MOD(1+D18,2),D18)</f>
-        <v>1</v>
-      </c>
-      <c r="R18" s="3">
-        <f ca="1">+IF(AND(R16=1,E16=1),MOD(1+E18,2),E18)</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-    </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="1">
-        <f ca="1">+MOD(D18+D14,2)</f>
-        <v>1</v>
-      </c>
-      <c r="E20" s="1">
-        <f ca="1">+MOD(E18+F14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="14"/>
-      <c r="O20" s="1">
-        <f ca="1">+MOD(O14+SUMPRODUCT(Q18:T18,Q20:T20),2)</f>
-        <v>0</v>
-      </c>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="1">
-        <f ca="1">+MOD(Q14+R14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="1">
-        <f ca="1">+MOD(S14+T14,2)</f>
-        <v>1</v>
-      </c>
-      <c r="S20" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
-    </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="1">
-        <f ca="1">+MOD(D20+E20,2)</f>
-        <v>1</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N22" s="14"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="1">
-        <f ca="1">+IF(AND(NOT(Q20),R20),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
-      <c r="U22" s="13"/>
-      <c r="V22" s="13"/>
-      <c r="W22" s="13"/>
-      <c r="X22" s="13"/>
-    </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="3">
-        <f ca="1">+ROUND(RAND(),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="N24" s="14"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="3">
-        <f ca="1">+IF(AND(Q22=1,D22=1),MOD(1+D24,2),D24)</f>
-        <v>1</v>
-      </c>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-      <c r="U24" s="13"/>
-      <c r="V24" s="13"/>
-      <c r="W24" s="13"/>
-      <c r="X24" s="13"/>
-    </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="1">
-        <f ca="1">+MOD(D24+D20,2)</f>
-        <v>1</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="14"/>
-      <c r="O26" s="1">
-        <f ca="1">+MOD(O20+SUMPRODUCT(Q24:T24,Q26:T26),2)</f>
-        <v>1</v>
-      </c>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="1">
-        <f ca="1">+MOD(Q20+R20,2)</f>
-        <v>1</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="S26" s="13"/>
-      <c r="T26" s="13"/>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="13"/>
-    </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-    </row>
-    <row r="28" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="2">
-        <f ca="1">+D26</f>
-        <v>1</v>
-      </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="N28" s="14"/>
-      <c r="O28" s="4">
-        <f ca="1">+O26</f>
-        <v>1</v>
-      </c>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-    </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-    </row>
-    <row r="30" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="N30" s="11"/>
-      <c r="O30" s="12" t="b">
-        <f ca="1">+O26=SUMPRODUCT(Q8:X8,D8:K8)</f>
-        <v>1</v>
-      </c>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
-      <c r="R30" s="13"/>
-      <c r="S30" s="13"/>
-      <c r="T30" s="13"/>
-      <c r="U30" s="13"/>
-      <c r="V30" s="13"/>
-      <c r="W30" s="13"/>
-      <c r="X30" s="13"/>
-    </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L31" s="14"/>
-    </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="33" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+      <c r="K40" t="s">
+        <v>33</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="M40" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="N40" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="G41">
+        <f>+C41*E41+(1-C41)*(1-E41)</f>
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="I41">
+        <f>+C41*C41+(1-C41)*(1-C41)</f>
+        <v>1</v>
+      </c>
+      <c r="K41" s="17">
+        <f>+K32</f>
+        <v>1</v>
+      </c>
+      <c r="L41" s="13">
+        <v>0.59819999999999995</v>
+      </c>
+      <c r="M41">
+        <f>+G41</f>
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="N41">
+        <f>+I41*$Y$33+(1-I41)*(1-$Y$33)</f>
+        <v>0.6875</v>
+      </c>
+      <c r="O41">
+        <f>+N32</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="42" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C42">
+        <v>0.9</v>
+      </c>
+      <c r="E42">
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="G42">
+        <f t="shared" ref="G42:G46" si="8">+C42*E42+(1-C42)*(1-E42)</f>
+        <v>0.60936000000000001</v>
+      </c>
+      <c r="I42">
+        <f t="shared" ref="I42:I46" si="9">+C42*C42+(1-C42)*(1-C42)</f>
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="K42" s="17">
+        <f t="shared" ref="K42:K46" si="10">+K33</f>
+        <v>0.70480000000000009</v>
+      </c>
+      <c r="L42" s="13">
+        <v>0.59819999999999995</v>
+      </c>
+      <c r="M42">
+        <f t="shared" ref="M42:M46" si="11">+G42</f>
+        <v>0.60936000000000001</v>
+      </c>
+      <c r="N42">
+        <f t="shared" ref="N42:N46" si="12">+I42*$Y$33+(1-I42)*(1-$Y$33)</f>
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="O42" s="19">
+        <f t="shared" ref="O42:O46" si="13">+N33</f>
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="43" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C43">
+        <v>0.8</v>
+      </c>
+      <c r="E43">
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="8"/>
+        <v>0.58201999999999998</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="9"/>
+        <v>0.68000000000000016</v>
+      </c>
+      <c r="K43" s="17">
+        <f t="shared" si="10"/>
+        <v>0.56480000000000008</v>
+      </c>
+      <c r="L43" s="13">
+        <v>0.59819999999999995</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="11"/>
+        <v>0.58201999999999998</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="12"/>
+        <v>0.56750000000000012</v>
+      </c>
+      <c r="O43" s="19">
+        <f t="shared" si="13"/>
+        <v>0.55400000000000005</v>
+      </c>
+    </row>
+    <row r="44" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C44">
+        <v>0.7</v>
+      </c>
+      <c r="E44">
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="8"/>
+        <v>0.55467999999999995</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="9"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="K44" s="17">
+        <f t="shared" si="10"/>
+        <v>0.51279999999999992</v>
+      </c>
+      <c r="L44" s="13">
+        <v>0.59819999999999995</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="11"/>
+        <v>0.55467999999999995</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="12"/>
+        <v>0.53</v>
+      </c>
+      <c r="O44" s="19">
+        <f t="shared" si="13"/>
+        <v>0.51600000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C45">
+        <v>0.6</v>
+      </c>
+      <c r="E45">
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="8"/>
+        <v>0.52734000000000003</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="9"/>
+        <v>0.52</v>
+      </c>
+      <c r="K45" s="17">
+        <f t="shared" si="10"/>
+        <v>0.50080000000000002</v>
+      </c>
+      <c r="L45" s="13">
+        <v>0.59819999999999995</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="11"/>
+        <v>0.52734000000000003</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="12"/>
+        <v>0.50750000000000006</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="13"/>
+        <v>0.502</v>
+      </c>
+    </row>
+    <row r="46" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C46">
+        <v>0.5</v>
+      </c>
+      <c r="E46">
+        <v>0.63670000000000004</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="8"/>
+        <v>0.5</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="K46" s="17">
+        <f t="shared" si="10"/>
+        <v>0.5</v>
+      </c>
+      <c r="L46" s="13">
+        <v>0.59819999999999995</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="11"/>
+        <v>0.5</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1552,17 +1594,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AH33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416556D7-58A6-4D7F-ACA7-4D6F236A6CDA}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:AD33"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="12" max="12" width="8.88671875" style="13"/>
     <col min="25" max="30" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13"/>
       <c r="B2" s="13" t="s">
         <v>8</v>
@@ -1570,7 +1612,7 @@
       <c r="C2" s="13"/>
       <c r="D2" s="5">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="6">
         <f t="shared" ref="E2:K2" ca="1" si="0">+ROUND(RAND(),0)</f>
@@ -1586,7 +1628,7 @@
       </c>
       <c r="H2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -1594,44 +1636,44 @@
       </c>
       <c r="J2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="7">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
-      <c r="Q2" s="15">
-        <v>0</v>
-      </c>
-      <c r="R2" s="15">
-        <v>1</v>
-      </c>
-      <c r="S2" s="15">
+      <c r="Q2" s="14">
+        <v>0</v>
+      </c>
+      <c r="R2" s="14">
+        <v>1</v>
+      </c>
+      <c r="S2" s="14">
         <v>2</v>
       </c>
-      <c r="T2" s="15">
+      <c r="T2" s="14">
         <v>3</v>
       </c>
-      <c r="U2" s="15">
+      <c r="U2" s="14">
         <v>4</v>
       </c>
-      <c r="V2" s="15">
+      <c r="V2" s="14">
         <v>5</v>
       </c>
-      <c r="W2" s="15">
+      <c r="W2" s="14">
         <v>6</v>
       </c>
-      <c r="X2" s="15">
+      <c r="X2" s="14">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="13" t="s">
         <v>9</v>
@@ -1639,7 +1681,7 @@
       <c r="C3" s="13"/>
       <c r="D3" s="8">
         <f ca="1">+RANDBETWEEN(0,7)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
@@ -1661,7 +1703,7 @@
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
     </row>
-    <row r="4" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13"/>
       <c r="B4" s="13" t="s">
         <v>15</v>
@@ -1691,51 +1733,17 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
     </row>
-    <row r="5" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-    </row>
-    <row r="6" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="14"/>
-    </row>
-    <row r="7" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="15">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15">
-        <v>1</v>
-      </c>
-      <c r="F7" s="15">
-        <v>2</v>
-      </c>
-      <c r="G7" s="15">
-        <v>3</v>
-      </c>
-      <c r="H7" s="15">
-        <v>4</v>
-      </c>
-      <c r="I7" s="15">
-        <v>5</v>
-      </c>
-      <c r="J7" s="15">
-        <v>6</v>
-      </c>
-      <c r="K7" s="15">
-        <v>7</v>
-      </c>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
         <v>0</v>
@@ -1743,7 +1751,7 @@
       <c r="C8" s="13"/>
       <c r="D8" s="1">
         <f ca="1">+D2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" ref="E8:K8" ca="1" si="1">+E2</f>
@@ -1759,7 +1767,7 @@
       </c>
       <c r="H8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -1767,25 +1775,24 @@
       </c>
       <c r="J8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="14"/>
+      <c r="N8" s="13"/>
       <c r="O8" s="9">
         <f ca="1">+D28</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="1">
         <f ca="1">+IF(Q2=$D3,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" ref="R8:X8" ca="1" si="2">+IF(R2=$D3,1,0)</f>
@@ -1813,21 +1820,11 @@
       </c>
       <c r="X8" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="H9" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="U9" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
         <v>1</v>
@@ -1835,7 +1832,7 @@
       <c r="C10" s="13"/>
       <c r="D10" s="1">
         <f ca="1">+MOD(D8+E8,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <f ca="1">+MOD(F8+G8,2)</f>
@@ -1843,11 +1840,11 @@
       </c>
       <c r="F10" s="1">
         <f ca="1">+MOD(H8+I8,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
         <f ca="1">+MOD(J8+K8,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>11</v>
@@ -1855,11 +1852,10 @@
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="14"/>
+      <c r="M10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="13"/>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
       <c r="Q10" s="1">
@@ -1876,7 +1872,7 @@
       </c>
       <c r="T10" s="1">
         <f ca="1">+IF(AND(NOT(W8),X8),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" s="13" t="s">
         <v>13</v>
@@ -1885,11 +1881,774 @@
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
     </row>
-    <row r="11" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-    </row>
+    <row r="11" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="3">
+        <f ca="1">+ROUND(RAND(),0)</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" ref="E12:G12" ca="1" si="3">+ROUND(RAND(),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="M12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="3">
+        <f ca="1">+IF(AND(Q10=1,D10=1),MOD(1+D12,2),D12)</f>
+        <v>1</v>
+      </c>
+      <c r="R12" s="3">
+        <f ca="1">+IF(AND(R10=1,E10=1),MOD(1+E12,2),E12)</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <f ca="1">+IF(AND(S10=1,F10=1),MOD(1+F12,2),F12)</f>
+        <v>1</v>
+      </c>
+      <c r="T12" s="3">
+        <f ca="1">+IF(AND(T10=1,G10=1),MOD(1+G12,2),G12)</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+    </row>
+    <row r="13" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="1">
+        <f ca="1">+MOD(D12+D8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <f ca="1">+MOD(E12+F8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <f ca="1">+MOD(F12+H8,2)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <f ca="1">+MOD(G12+J8,2)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="M14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="1">
+        <f ca="1">+MOD(O8+SUMPRODUCT(Q12:T12,Q14:T14),2)</f>
+        <v>1</v>
+      </c>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="1">
+        <f ca="1">+MOD(Q8+R8,2)</f>
+        <v>1</v>
+      </c>
+      <c r="R14" s="1">
+        <f ca="1">+MOD(S8+T8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <f ca="1">+MOD(U8+V8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <f ca="1">+MOD(W8+X8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+    </row>
+    <row r="15" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="1">
+        <f ca="1">+MOD(D14+E14,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <f ca="1">+MOD(F14+G14,2)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="M16" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="1">
+        <f ca="1">+IF(AND(NOT(Q14),R14),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <f ca="1">+IF(AND(NOT(S14),T14),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="T16" s="13"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
+    </row>
+    <row r="17" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="3">
+        <f ca="1">+ROUND(RAND(),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" ref="E18" ca="1" si="4">+ROUND(RAND(),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="M18" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="3">
+        <f ca="1">+IF(AND(Q16=1,D16=1),MOD(1+D18,2),D18)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
+        <f ca="1">+IF(AND(R16=1,E16=1),MOD(1+E18,2),E18)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+    </row>
+    <row r="19" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="1">
+        <f ca="1">+MOD(D18+D14,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <f ca="1">+MOD(E18+F14,2)</f>
+        <v>1</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="M20" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="1">
+        <f ca="1">+MOD(O14+SUMPRODUCT(Q18:T18,Q20:T20),2)</f>
+        <v>1</v>
+      </c>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="1">
+        <f ca="1">+MOD(Q14+R14,2)</f>
+        <v>1</v>
+      </c>
+      <c r="R20" s="1">
+        <f ca="1">+MOD(S14+T14,2)</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+    </row>
+    <row r="21" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="1">
+        <f ca="1">+MOD(D20+E20,2)</f>
+        <v>1</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="M22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="1">
+        <f ca="1">+IF(AND(NOT(Q20),R20),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S22" s="13"/>
+      <c r="T22" s="13"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+    </row>
+    <row r="23" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="3">
+        <f ca="1">+ROUND(RAND(),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="M24" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="3">
+        <f ca="1">+IF(AND(Q22=1,D22=1),MOD(1+D24,2),D24)</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+    </row>
+    <row r="25" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="1">
+        <f ca="1">+MOD(D24+D20,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="M26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="1">
+        <f ca="1">+MOD(O20+SUMPRODUCT(Q24:T24,Q26:T26),2)</f>
+        <v>1</v>
+      </c>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="1">
+        <f ca="1">+MOD(Q20+R20,2)</f>
+        <v>1</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="S26" s="13"/>
+      <c r="T26" s="13"/>
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+    </row>
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="2">
+        <f ca="1">+D26</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="M28" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="4">
+        <f ca="1">+O26</f>
+        <v>1</v>
+      </c>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+    </row>
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="M30" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" s="11"/>
+      <c r="O30" s="12" t="b">
+        <f ca="1">+O26=SUMPRODUCT(Q8:X8,D8:K8)</f>
+        <v>1</v>
+      </c>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+    </row>
+    <row r="31" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="33" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:AH33"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="8.88671875" style="13"/>
+    <col min="25" max="30" width="8.88671875" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="5">
+        <f ca="1">+ROUND(RAND(),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="6">
+        <f t="shared" ref="E2:K2" ca="1" si="0">+ROUND(RAND(),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I2" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="14">
+        <v>0</v>
+      </c>
+      <c r="R2" s="14">
+        <v>1</v>
+      </c>
+      <c r="S2" s="14">
+        <v>2</v>
+      </c>
+      <c r="T2" s="14">
+        <v>3</v>
+      </c>
+      <c r="U2" s="14">
+        <v>4</v>
+      </c>
+      <c r="V2" s="14">
+        <v>5</v>
+      </c>
+      <c r="W2" s="14">
+        <v>6</v>
+      </c>
+      <c r="X2" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="8">
+        <f ca="1">+RANDBETWEEN(0,7)</f>
+        <v>2</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+    </row>
+    <row r="4" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="4">
+        <f ca="1">+OFFSET(D2,0,D3)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+    </row>
+    <row r="5" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14">
+        <v>2</v>
+      </c>
+      <c r="G7" s="14">
+        <v>3</v>
+      </c>
+      <c r="H7" s="14">
+        <v>4</v>
+      </c>
+      <c r="I7" s="14">
+        <v>5</v>
+      </c>
+      <c r="J7" s="14">
+        <v>6</v>
+      </c>
+      <c r="K7" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="1">
+        <f ca="1">+D2</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" ref="E8:K8" ca="1" si="1">+E2</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="9">
+        <f ca="1">+D28</f>
+        <v>1</v>
+      </c>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="1">
+        <f ca="1">+IF(Q2=$D3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <f t="shared" ref="R8:X8" ca="1" si="2">+IF(R2=$D3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="1">
+        <f ca="1">+MOD(D8+E8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <f ca="1">+MOD(F8+G8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <f ca="1">+MOD(H8+I8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <f ca="1">+MOD(J8+K8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="M10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="1">
+        <f ca="1">+IF(AND(NOT(Q8),R8),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <f ca="1">+IF(AND(NOT(S8),T8),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <f ca="1">+IF(AND(NOT(U8),V8),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <f ca="1">+IF(AND(NOT(W8),X8),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+    </row>
+    <row r="11" spans="1:34" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="13" t="s">
@@ -1898,7 +2657,7 @@
       <c r="C12" s="13"/>
       <c r="D12" s="3">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" ref="E12:G12" ca="1" si="3">+ROUND(RAND(),0)</f>
@@ -1916,16 +2675,15 @@
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14" t="s">
+      <c r="M12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="14"/>
+      <c r="N12" s="13"/>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
       <c r="Q12" s="3">
         <f ca="1">+IF(AND(Q10=1,D10=1),MOD(1+D12,2),D12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="3">
         <f ca="1">+IF(AND(R10=1,E10=1),MOD(1+E12,2),E12)</f>
@@ -1937,7 +2695,7 @@
       </c>
       <c r="T12" s="3">
         <f ca="1">+IF(AND(T10=1,G10=1),MOD(1+G12,2),G12)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" s="13"/>
       <c r="V12" s="13"/>
@@ -1964,9 +2722,6 @@
       <c r="H13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
@@ -1976,7 +2731,7 @@
       <c r="C14" s="13"/>
       <c r="D14" s="1">
         <f ca="1">+MOD(1+D12+D8,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <f ca="1">+MOD(1+E12+F8,2)</f>
@@ -1984,7 +2739,7 @@
       </c>
       <c r="F14" s="1">
         <f ca="1">+MOD(1+F12+H8,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
         <f ca="1">+MOD(1+G12+J8,2)</f>
@@ -1996,11 +2751,10 @@
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="14"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="1">
         <f ca="1">+MOD(O8+SUMPRODUCT(Q12:T12,Q14:T14),2)</f>
         <v>0</v>
@@ -2012,7 +2766,7 @@
       </c>
       <c r="R14" s="1">
         <f ca="1">+MOD(S8+T8,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="1">
         <f ca="1">+MOD(U8+V8,2)</f>
@@ -2020,7 +2774,7 @@
       </c>
       <c r="T14" s="1">
         <f ca="1">+MOD(W8+X8,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" s="13" t="s">
         <v>14</v>
@@ -2033,9 +2787,6 @@
       <c r="F15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
@@ -2045,11 +2796,11 @@
       <c r="C16" s="13"/>
       <c r="D16" s="1">
         <f ca="1">+MOD(D14+E14,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
         <f ca="1">+MOD(F14+G14,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>11</v>
@@ -2059,20 +2810,19 @@
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" s="14"/>
+      <c r="M16" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
       <c r="Q16" s="1">
         <f ca="1">+IF(AND(NOT(Q14),R14),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="1">
         <f ca="1">+IF(AND(NOT(S14),T14),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="13" t="s">
         <v>13</v>
@@ -2083,11 +2833,7 @@
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
     </row>
-    <row r="17" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-    </row>
+    <row r="17" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="13" t="s">
@@ -2108,11 +2854,10 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14" t="s">
+      <c r="M18" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N18" s="14"/>
+      <c r="N18" s="13"/>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
       <c r="Q18" s="3">
@@ -2121,7 +2866,7 @@
       </c>
       <c r="R18" s="3">
         <f ca="1">+IF(AND(R16=1,E16=1),MOD(1+E18,2),E18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="13"/>
       <c r="T18" s="13"/>
@@ -2142,9 +2887,6 @@
       <c r="F19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
@@ -2154,11 +2896,11 @@
       <c r="C20" s="13"/>
       <c r="D20" s="1">
         <f ca="1">+MOD(1+D18+D14,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1">
         <f ca="1">+MOD(1+E18+F14,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>18</v>
@@ -2168,11 +2910,10 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14" t="s">
+      <c r="M20" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="14"/>
+      <c r="N20" s="13"/>
       <c r="O20" s="1">
         <f ca="1">+MOD(O14+SUMPRODUCT(Q18:T18,Q20:T20),2)</f>
         <v>0</v>
@@ -2180,11 +2921,11 @@
       <c r="P20" s="13"/>
       <c r="Q20" s="1">
         <f ca="1">+MOD(Q14+R14,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="1">
         <f ca="1">+MOD(S14+T14,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="13" t="s">
         <v>14</v>
@@ -2199,9 +2940,6 @@
       <c r="E21" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
@@ -2222,16 +2960,15 @@
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N22" s="14"/>
+      <c r="M22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
       <c r="Q22" s="1">
         <f ca="1">+IF(AND(NOT(Q20),R20),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="13" t="s">
         <v>13</v>
@@ -2243,11 +2980,7 @@
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
     </row>
-    <row r="23" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-    </row>
+    <row r="23" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="13" t="s">
@@ -2256,7 +2989,7 @@
       <c r="C24" s="13"/>
       <c r="D24" s="3">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
@@ -2265,16 +2998,15 @@
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14" t="s">
+      <c r="M24" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N24" s="14"/>
+      <c r="N24" s="13"/>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="3">
         <f ca="1">+IF(AND(Q22=1,D22=1),MOD(1+D24,2),D24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="13"/>
       <c r="S24" s="13"/>
@@ -2292,9 +3024,6 @@
       <c r="E25" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
@@ -2313,14 +3042,13 @@
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14" t="s">
+      <c r="M26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="14"/>
+      <c r="N26" s="13"/>
       <c r="O26" s="1">
         <f ca="1">+MOD(O20+SUMPRODUCT(Q24:T24,Q26:T26),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="13"/>
       <c r="Q26" s="1">
@@ -2337,11 +3065,7 @@
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
     </row>
-    <row r="27" spans="1:32" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-    </row>
+    <row r="27" spans="1:32" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
@@ -2359,14 +3083,13 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14" t="s">
+      <c r="M28" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N28" s="14"/>
+      <c r="N28" s="13"/>
       <c r="O28" s="4">
         <f ca="1">+O26</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
@@ -2379,18 +3102,14 @@
       <c r="X28" s="13"/>
       <c r="AE28">
         <f ca="1">+SUM(O8+SUMPRODUCT(Q12:T12,Q14:T14)+SUMPRODUCT(Q18:R18,Q20:R20)+Q24)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="b">
         <f ca="1">+MOD(AE28+O28,2)=0</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-    </row>
+    <row r="29" spans="1:32" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
@@ -2403,7 +3122,6 @@
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
-      <c r="L30" s="14"/>
       <c r="M30" s="10" t="s">
         <v>17</v>
       </c>
@@ -2422,9 +3140,7 @@
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
     </row>
-    <row r="31" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L31" s="14"/>
-    </row>
+    <row r="31" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:32" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="33" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2433,7 +3149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB27F4F-1578-4325-B004-87F10D112CEC}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:AJ42"/>
@@ -2452,11 +3168,11 @@
       </c>
       <c r="E2" s="6">
         <f t="shared" ref="E2:S2" ca="1" si="0">+ROUND(RAND(),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -2464,11 +3180,11 @@
       </c>
       <c r="H2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -2476,7 +3192,7 @@
       </c>
       <c r="K2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -2484,7 +3200,7 @@
       </c>
       <c r="M2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -2492,7 +3208,7 @@
       </c>
       <c r="O2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -2500,15 +3216,15 @@
       </c>
       <c r="Q2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="13"/>
       <c r="U2" s="13"/>
@@ -2534,9 +3250,9 @@
         <v>9</v>
       </c>
       <c r="C3" s="13"/>
-      <c r="D3" s="16">
+      <c r="D3" s="15">
         <f ca="1">+RANDBETWEEN(0,15)</f>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
@@ -2579,7 +3295,7 @@
       <c r="C4" s="13"/>
       <c r="D4" s="4">
         <f ca="1">+OFFSET(D2,0,D3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -2626,9 +3342,9 @@
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
@@ -2664,9 +3380,9 @@
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
@@ -2702,9 +3418,9 @@
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -2740,9 +3456,9 @@
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -2778,65 +3494,65 @@
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="15" t="s">
+      <c r="L9" s="13"/>
+      <c r="M9" s="14" t="s">
         <v>10</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
-      <c r="Q9" s="15">
-        <v>0</v>
-      </c>
-      <c r="R9" s="15">
-        <v>1</v>
-      </c>
-      <c r="S9" s="15">
+      <c r="Q9" s="14">
+        <v>0</v>
+      </c>
+      <c r="R9" s="14">
+        <v>1</v>
+      </c>
+      <c r="S9" s="14">
         <v>2</v>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="14">
         <v>3</v>
       </c>
-      <c r="U9" s="15">
+      <c r="U9" s="14">
         <v>4</v>
       </c>
-      <c r="V9" s="15">
+      <c r="V9" s="14">
         <v>5</v>
       </c>
-      <c r="W9" s="15">
+      <c r="W9" s="14">
         <v>6</v>
       </c>
-      <c r="X9" s="15">
+      <c r="X9" s="14">
         <v>7</v>
       </c>
-      <c r="Y9" s="15">
+      <c r="Y9" s="14">
         <v>8</v>
       </c>
-      <c r="Z9" s="15">
+      <c r="Z9" s="14">
         <v>9</v>
       </c>
-      <c r="AA9" s="15">
+      <c r="AA9" s="14">
         <v>10</v>
       </c>
-      <c r="AB9" s="15">
+      <c r="AB9" s="14">
         <v>11</v>
       </c>
-      <c r="AC9" s="15">
+      <c r="AC9" s="14">
         <v>12</v>
       </c>
-      <c r="AD9" s="15">
+      <c r="AD9" s="14">
         <v>13</v>
       </c>
-      <c r="AE9" s="15">
+      <c r="AE9" s="14">
         <v>14</v>
       </c>
-      <c r="AF9" s="15">
+      <c r="AF9" s="14">
         <v>15</v>
       </c>
-      <c r="AG9" s="15"/>
-      <c r="AH9" s="15"/>
-      <c r="AI9" s="15"/>
-      <c r="AJ9" s="15"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
@@ -2850,11 +3566,11 @@
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14" t="s">
+      <c r="L10" s="13"/>
+      <c r="M10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N10" s="14"/>
+      <c r="N10" s="13"/>
       <c r="O10" s="9">
         <f ca="1">+D38</f>
         <v>1</v>
@@ -2878,7 +3594,7 @@
       </c>
       <c r="U10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -2922,7 +3638,7 @@
       </c>
       <c r="AF10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" s="13"/>
       <c r="AH10" s="13"/>
@@ -2933,52 +3649,52 @@
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="15">
-        <v>1</v>
-      </c>
-      <c r="F11" s="15">
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14">
         <v>2</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="14">
         <v>3</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="14">
         <v>4</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="14">
         <v>5</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="14">
         <v>6</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="14">
         <v>7</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="14">
         <v>8</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="14">
         <v>9</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="14">
         <v>10</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="14">
         <v>11</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="14">
         <v>12</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="14">
         <v>13</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="14">
         <v>14</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="14">
         <v>15</v>
       </c>
       <c r="T11" s="13"/>
@@ -3011,11 +3727,11 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" ref="E12:S12" ca="1" si="2">+E2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -3023,11 +3739,11 @@
       </c>
       <c r="H12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -3035,7 +3751,7 @@
       </c>
       <c r="K12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -3043,7 +3759,7 @@
       </c>
       <c r="M12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -3051,7 +3767,7 @@
       </c>
       <c r="O12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -3059,15 +3775,15 @@
       </c>
       <c r="Q12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="13"/>
       <c r="U12" s="13"/>
@@ -3099,9 +3815,9 @@
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
@@ -3133,11 +3849,11 @@
       <c r="C14" s="13"/>
       <c r="D14" s="1">
         <f ca="1">+MOD(D12+E12,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="1">
         <f ca="1">+MOD(F12+G12,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1">
         <f ca="1">+MOD(H12+I12,2)</f>
@@ -3145,29 +3861,29 @@
       </c>
       <c r="G14" s="1">
         <f ca="1">+MOD(J12+K12,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
         <f ca="1">+MOD(L12+M12,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
         <f ca="1">+MOD(N12+O12,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1">
         <f ca="1">+MOD(P12+Q12,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
         <f ca="1">+MOD(R12+S12,2)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N14" s="14"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="13"/>
       <c r="O14" s="13"/>
       <c r="P14" s="13"/>
       <c r="Q14" s="1">
@@ -3200,7 +3916,7 @@
       </c>
       <c r="X14" s="1">
         <f ca="1">+IF(AND(NOT(AE10),AF10),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="13"/>
       <c r="Z14" s="13"/>
@@ -3227,9 +3943,9 @@
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
       <c r="O15" s="13"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
@@ -3269,7 +3985,7 @@
       </c>
       <c r="F16" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" ca="1" si="3"/>
@@ -3277,7 +3993,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" ca="1" si="3"/>
@@ -3285,49 +4001,49 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3">
         <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14" t="s">
+      <c r="L16" s="13"/>
+      <c r="M16" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N16" s="14"/>
+      <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
       <c r="Q16" s="3">
-        <f ca="1">+IF(AND(Q14=1,D14=1),MOD(1+D16,2),D16)</f>
+        <f t="shared" ref="Q16:X16" ca="1" si="4">+IF(AND(Q14=1,D14=1),MOD(1+D16,2),D16)</f>
         <v>1</v>
       </c>
       <c r="R16" s="3">
-        <f ca="1">+IF(AND(R14=1,E14=1),MOD(1+E16,2),E16)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="S16" s="3">
-        <f ca="1">+IF(AND(S14=1,F14=1),MOD(1+F16,2),F16)</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="T16" s="3">
-        <f ca="1">+IF(AND(T14=1,G14=1),MOD(1+G16,2),G16)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="U16" s="3">
-        <f ca="1">+IF(AND(U14=1,H14=1),MOD(1+H16,2),H16)</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="V16" s="3">
-        <f ca="1">+IF(AND(V14=1,I14=1),MOD(1+I16,2),I16)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="W16" s="3">
-        <f ca="1">+IF(AND(W14=1,J14=1),MOD(1+J16,2),J16)</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="X16" s="3">
-        <f ca="1">+IF(AND(X14=1,K14=1),MOD(1+K16,2),K16)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="Y16" s="13"/>
@@ -3355,9 +4071,9 @@
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
       <c r="O17" s="13"/>
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
@@ -3393,7 +4109,7 @@
       </c>
       <c r="E18" s="1">
         <f ca="1">+MOD(E16+F12,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1">
         <f ca="1">+MOD(F16+H12,2)</f>
@@ -3405,7 +4121,7 @@
       </c>
       <c r="H18" s="1">
         <f ca="1">+MOD(H16+L12,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="1">
         <f ca="1">+MOD(I16+N12,2)</f>
@@ -3413,17 +4129,17 @@
       </c>
       <c r="J18" s="1">
         <f ca="1">+MOD(J16+P12,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
         <f ca="1">+MOD(K16+R12,2)</f>
-        <v>1</v>
-      </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="14"/>
+      <c r="N18" s="13"/>
       <c r="O18" s="1">
         <f ca="1">+MOD(O10+SUMPRODUCT(Q16:X16,Q18:X18),2)</f>
         <v>0</v>
@@ -3439,7 +4155,7 @@
       </c>
       <c r="S18" s="1">
         <f ca="1">+MOD(U10+V10,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" s="1">
         <f ca="1">+MOD(W10+X10,2)</f>
@@ -3459,7 +4175,7 @@
       </c>
       <c r="X18" s="1">
         <f ca="1">+MOD(AE10+AF10,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="13"/>
       <c r="Z18" s="13"/>
@@ -3486,9 +4202,9 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
@@ -3520,7 +4236,7 @@
       <c r="C20" s="13"/>
       <c r="D20" s="1">
         <f ca="1">+MOD(D18+E18,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <f ca="1">+MOD(F18+G18,2)</f>
@@ -3528,7 +4244,7 @@
       </c>
       <c r="F20" s="1">
         <f ca="1">+MOD(H18+I18,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <f ca="1">+MOD(J18+K18,2)</f>
@@ -3540,11 +4256,11 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N20" s="14"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N20" s="13"/>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="1">
@@ -3561,7 +4277,7 @@
       </c>
       <c r="T20" s="1">
         <f ca="1">+IF(AND(NOT(W18),X18),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" s="13" t="s">
         <v>13</v>
@@ -3594,9 +4310,9 @@
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
@@ -3631,26 +4347,26 @@
         <v>1</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" ref="E22:G22" ca="1" si="4">+ROUND(RAND(),0)</f>
-        <v>0</v>
+        <f t="shared" ref="E22:G22" ca="1" si="5">+ROUND(RAND(),0)</f>
+        <v>1</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14" t="s">
+      <c r="L22" s="13"/>
+      <c r="M22" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N22" s="14"/>
+      <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
       <c r="Q22" s="3">
@@ -3659,7 +4375,7 @@
       </c>
       <c r="R22" s="3">
         <f ca="1">+IF(AND(R20=1,E20=1),MOD(1+E22,2),E22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="3">
         <f ca="1">+IF(AND(S20=1,F20=1),MOD(1+F22,2),F22)</f>
@@ -3667,7 +4383,7 @@
       </c>
       <c r="T22" s="3">
         <f ca="1">+IF(AND(T20=1,G20=1),MOD(1+G22,2),G22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" s="13"/>
       <c r="V22" s="13"/>
@@ -3698,9 +4414,9 @@
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
@@ -3736,11 +4452,11 @@
       </c>
       <c r="E24" s="1">
         <f ca="1">+MOD(E22+F18,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1">
         <f ca="1">+MOD(F22+H18,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1">
         <f ca="1">+MOD(G22+J18,2)</f>
@@ -3752,14 +4468,14 @@
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14" t="s">
+      <c r="L24" s="13"/>
+      <c r="M24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="14"/>
+      <c r="N24" s="13"/>
       <c r="O24" s="1">
         <f ca="1">+MOD(O18+SUMPRODUCT(Q22:T22,Q24:T24),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="13"/>
       <c r="Q24" s="1">
@@ -3768,7 +4484,7 @@
       </c>
       <c r="R24" s="1">
         <f ca="1">+MOD(S18+T18,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" s="1">
         <f ca="1">+MOD(U18+V18,2)</f>
@@ -3776,7 +4492,7 @@
       </c>
       <c r="T24" s="1">
         <f ca="1">+MOD(W18+X18,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" s="13" t="s">
         <v>14</v>
@@ -3809,9 +4525,9 @@
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
@@ -3843,11 +4559,11 @@
       <c r="C26" s="13"/>
       <c r="D26" s="1">
         <f ca="1">+MOD(D24+E24,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="1">
         <f ca="1">+MOD(F24+G24,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="13" t="s">
         <v>11</v>
@@ -3857,20 +4573,20 @@
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N26" s="14"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N26" s="13"/>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
       <c r="Q26" s="1">
         <f ca="1">+IF(AND(NOT(Q24),R24),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" s="1">
         <f ca="1">+IF(AND(NOT(S24),T24),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="13" t="s">
         <v>13</v>
@@ -3905,9 +4621,9 @@
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -3939,10 +4655,10 @@
       <c r="C28" s="13"/>
       <c r="D28" s="3">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" ref="E28" ca="1" si="5">+ROUND(RAND(),0)</f>
+        <f t="shared" ref="E28" ca="1" si="6">+ROUND(RAND(),0)</f>
         <v>0</v>
       </c>
       <c r="F28" s="13"/>
@@ -3951,16 +4667,16 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14" t="s">
+      <c r="L28" s="13"/>
+      <c r="M28" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N28" s="14"/>
+      <c r="N28" s="13"/>
       <c r="O28" s="13"/>
       <c r="P28" s="13"/>
       <c r="Q28" s="3">
         <f ca="1">+IF(AND(Q26=1,D26=1),MOD(1+D28,2),D28)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" s="3">
         <f ca="1">+IF(AND(R26=1,E26=1),MOD(1+E28,2),E28)</f>
@@ -3997,9 +4713,9 @@
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
@@ -4031,11 +4747,11 @@
       <c r="C30" s="13"/>
       <c r="D30" s="1">
         <f ca="1">+MOD(D28+D24,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="1">
         <f ca="1">+MOD(E28+F24,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>12</v>
@@ -4045,11 +4761,11 @@
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14" t="s">
+      <c r="L30" s="13"/>
+      <c r="M30" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N30" s="14"/>
+      <c r="N30" s="13"/>
       <c r="O30" s="1">
         <f ca="1">+MOD(O24+SUMPRODUCT(Q28:T28,Q30:T30),2)</f>
         <v>1</v>
@@ -4057,11 +4773,11 @@
       <c r="P30" s="13"/>
       <c r="Q30" s="1">
         <f ca="1">+MOD(Q24+R24,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" s="1">
         <f ca="1">+MOD(S24+T24,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="13" t="s">
         <v>14</v>
@@ -4096,9 +4812,9 @@
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
@@ -4141,16 +4857,16 @@
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
       <c r="K32" s="13"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N32" s="14"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N32" s="13"/>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="1">
         <f ca="1">+IF(AND(NOT(Q30),R30),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="13" t="s">
         <v>13</v>
@@ -4186,9 +4902,9 @@
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
@@ -4220,7 +4936,7 @@
       <c r="C34" s="13"/>
       <c r="D34" s="3">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
@@ -4229,16 +4945,16 @@
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14" t="s">
+      <c r="L34" s="13"/>
+      <c r="M34" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N34" s="14"/>
+      <c r="N34" s="13"/>
       <c r="O34" s="13"/>
       <c r="P34" s="13"/>
       <c r="Q34" s="3">
         <f ca="1">+IF(AND(Q32=1,D32=1),MOD(1+D34,2),D34)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" s="13"/>
       <c r="S34" s="13"/>
@@ -4272,9 +4988,9 @@
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
       <c r="O35" s="13"/>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -4317,14 +5033,14 @@
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14" t="s">
+      <c r="L36" s="13"/>
+      <c r="M36" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N36" s="14"/>
+      <c r="N36" s="13"/>
       <c r="O36" s="1">
         <f ca="1">+MOD(O30+SUMPRODUCT(Q34:T34,Q36:T36),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" s="13"/>
       <c r="Q36" s="1">
@@ -4365,9 +5081,9 @@
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
@@ -4408,14 +5124,14 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="13"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14" t="s">
+      <c r="L38" s="13"/>
+      <c r="M38" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N38" s="14"/>
+      <c r="N38" s="13"/>
       <c r="O38" s="4">
         <f ca="1">+O36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
@@ -4451,9 +5167,9 @@
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
@@ -4489,7 +5205,7 @@
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
       <c r="K40" s="13"/>
-      <c r="L40" s="14"/>
+      <c r="L40" s="13"/>
       <c r="M40" s="10" t="s">
         <v>17</v>
       </c>
@@ -4532,7 +5248,7 @@
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
       <c r="K41" s="13"/>
-      <c r="L41" s="14"/>
+      <c r="L41" s="13"/>
       <c r="M41" s="13"/>
       <c r="N41" s="13"/>
       <c r="O41" s="13"/>
@@ -4602,7 +5318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AQ41"/>
@@ -4615,7 +5331,7 @@
       <c r="C1" s="13"/>
       <c r="D1" s="5">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="6">
         <f t="shared" ref="E1:S1" ca="1" si="0">+ROUND(RAND(),0)</f>
@@ -4627,27 +5343,27 @@
       </c>
       <c r="G1" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -4663,11 +5379,11 @@
       </c>
       <c r="P1" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q1" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -4700,9 +5416,9 @@
         <v>9</v>
       </c>
       <c r="C2" s="13"/>
-      <c r="D2" s="16">
+      <c r="D2" s="15">
         <f ca="1">+RANDBETWEEN(0,15)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
@@ -4744,7 +5460,7 @@
       <c r="C3" s="13"/>
       <c r="D3" s="4">
         <f ca="1">+OFFSET(D1,0,D2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
@@ -4791,9 +5507,9 @@
       <c r="I4" s="13"/>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="13"/>
@@ -4829,9 +5545,9 @@
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
@@ -4867,9 +5583,9 @@
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
@@ -4905,9 +5621,9 @@
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -4943,65 +5659,65 @@
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="15" t="s">
+      <c r="L8" s="13"/>
+      <c r="M8" s="14" t="s">
         <v>10</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
-      <c r="Q8" s="15">
-        <v>0</v>
-      </c>
-      <c r="R8" s="15">
-        <v>1</v>
-      </c>
-      <c r="S8" s="15">
+      <c r="Q8" s="14">
+        <v>0</v>
+      </c>
+      <c r="R8" s="14">
+        <v>1</v>
+      </c>
+      <c r="S8" s="14">
         <v>2</v>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="14">
         <v>3</v>
       </c>
-      <c r="U8" s="15">
+      <c r="U8" s="14">
         <v>4</v>
       </c>
-      <c r="V8" s="15">
+      <c r="V8" s="14">
         <v>5</v>
       </c>
-      <c r="W8" s="15">
+      <c r="W8" s="14">
         <v>6</v>
       </c>
-      <c r="X8" s="15">
+      <c r="X8" s="14">
         <v>7</v>
       </c>
-      <c r="Y8" s="15">
+      <c r="Y8" s="14">
         <v>8</v>
       </c>
-      <c r="Z8" s="15">
+      <c r="Z8" s="14">
         <v>9</v>
       </c>
-      <c r="AA8" s="15">
+      <c r="AA8" s="14">
         <v>10</v>
       </c>
-      <c r="AB8" s="15">
+      <c r="AB8" s="14">
         <v>11</v>
       </c>
-      <c r="AC8" s="15">
+      <c r="AC8" s="14">
         <v>12</v>
       </c>
-      <c r="AD8" s="15">
+      <c r="AD8" s="14">
         <v>13</v>
       </c>
-      <c r="AE8" s="15">
+      <c r="AE8" s="14">
         <v>14</v>
       </c>
-      <c r="AF8" s="15">
+      <c r="AF8" s="14">
         <v>15</v>
       </c>
-      <c r="AG8" s="15"/>
-      <c r="AH8" s="15"/>
-      <c r="AI8" s="15"/>
-      <c r="AJ8" s="15"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
+      <c r="AJ8" s="14"/>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
@@ -5015,11 +5731,11 @@
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14" t="s">
+      <c r="L9" s="13"/>
+      <c r="M9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="14"/>
+      <c r="N9" s="13"/>
       <c r="O9" s="9">
         <f ca="1">+D37</f>
         <v>1</v>
@@ -5031,7 +5747,7 @@
       </c>
       <c r="R9" s="1">
         <f t="shared" ref="R9:AF9" ca="1" si="1">+IF(R8=$D$2,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -5051,7 +5767,7 @@
       </c>
       <c r="W9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -5098,52 +5814,52 @@
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
-      <c r="D10" s="15">
-        <v>0</v>
-      </c>
-      <c r="E10" s="15">
-        <v>1</v>
-      </c>
-      <c r="F10" s="15">
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14">
         <v>2</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <v>3</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="14">
         <v>4</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="14">
         <v>5</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="14">
         <v>6</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="14">
         <v>7</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="14">
         <v>8</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="14">
         <v>9</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="14">
         <v>10</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="14">
         <v>11</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="14">
         <v>12</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="14">
         <v>13</v>
       </c>
-      <c r="R10" s="15">
+      <c r="R10" s="14">
         <v>14</v>
       </c>
-      <c r="S10" s="15">
+      <c r="S10" s="14">
         <v>15</v>
       </c>
       <c r="T10" s="13"/>
@@ -5172,7 +5888,7 @@
       <c r="C11" s="13"/>
       <c r="D11" s="1">
         <f ca="1">+D1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" ref="E11:S11" ca="1" si="2">+E1</f>
@@ -5184,27 +5900,27 @@
       </c>
       <c r="G11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -5220,11 +5936,11 @@
       </c>
       <c r="P11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -5264,9 +5980,9 @@
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
@@ -5298,11 +6014,11 @@
       <c r="C13" s="13"/>
       <c r="D13" s="1">
         <f ca="1">+MOD(D11+E11,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <f ca="1">+MOD(F11+G11,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1">
         <f ca="1">+MOD(H11+I11,2)</f>
@@ -5314,7 +6030,7 @@
       </c>
       <c r="H13" s="1">
         <f ca="1">+MOD(L11+M11,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1">
         <f ca="1">+MOD(N11+O11,2)</f>
@@ -5328,16 +6044,16 @@
         <f ca="1">+MOD(R11+S11,2)</f>
         <v>1</v>
       </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N13" s="14"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="13"/>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
       <c r="Q13" s="1">
         <f ca="1">+IF(AND(NOT(Q9),R9),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="1">
         <f ca="1">+IF(AND(NOT(S9),T9),1,0)</f>
@@ -5392,9 +6108,9 @@
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="13"/>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
@@ -5438,11 +6154,11 @@
       </c>
       <c r="G15" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" ca="1" si="3"/>
@@ -5454,46 +6170,46 @@
       </c>
       <c r="K15" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N15" s="14"/>
+      <c r="N15" s="13"/>
       <c r="O15" s="13"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="3">
-        <f ca="1">+IF(AND(Q13=1,D13=1),MOD(1+D15,2),D15)</f>
+        <f t="shared" ref="Q15:X15" ca="1" si="4">+IF(AND(Q13=1,D13=1),MOD(1+D15,2),D15)</f>
         <v>1</v>
       </c>
       <c r="R15" s="3">
-        <f ca="1">+IF(AND(R13=1,E13=1),MOD(1+E15,2),E15)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="S15" s="3">
-        <f ca="1">+IF(AND(S13=1,F13=1),MOD(1+F15,2),F15)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="T15" s="3">
-        <f ca="1">+IF(AND(T13=1,G13=1),MOD(1+G15,2),G15)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="U15" s="3">
-        <f ca="1">+IF(AND(U13=1,H13=1),MOD(1+H15,2),H15)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="V15" s="3">
-        <f ca="1">+IF(AND(V13=1,I13=1),MOD(1+I15,2),I15)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
       <c r="W15" s="3">
-        <f ca="1">+IF(AND(W13=1,J13=1),MOD(1+J15,2),J15)</f>
+        <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
       <c r="X15" s="3">
-        <f ca="1">+IF(AND(X13=1,K13=1),MOD(1+K15,2),K15)</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="Y15" s="13"/>
       <c r="Z15" s="13"/>
@@ -5511,31 +6227,31 @@
         <v>1</v>
       </c>
       <c r="AK15" t="b">
-        <f t="shared" ref="AK15:AQ15" ca="1" si="4">+IF(AND(E13=1,R13=1),NOT(E15=R15),E15=R15)</f>
+        <f t="shared" ref="AK15:AQ15" ca="1" si="5">+IF(AND(E13=1,R13=1),NOT(E15=R15),E15=R15)</f>
         <v>1</v>
       </c>
       <c r="AL15" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="AM15" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="AN15" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="AO15" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="AP15" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="AQ15" t="b">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -5551,9 +6267,9 @@
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
@@ -5585,7 +6301,7 @@
       <c r="C17" s="13"/>
       <c r="D17" s="1">
         <f ca="1">+MOD(1+D15+D11,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
         <f ca="1">+MOD(1+E15+F11,2)</f>
@@ -5593,7 +6309,7 @@
       </c>
       <c r="F17" s="1">
         <f ca="1">+MOD(1+F15+H11,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <f ca="1">+MOD(1+G15+J11,2)</f>
@@ -5609,25 +6325,25 @@
       </c>
       <c r="J17" s="1">
         <f ca="1">+MOD(1+J15+P11,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
         <f ca="1">+MOD(1+K15+R11,2)</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="14"/>
+      <c r="N17" s="13"/>
       <c r="O17" s="1">
         <f ca="1">+MOD(O9+SUMPRODUCT(Q15:X15,Q17:X17),2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="13"/>
       <c r="Q17" s="1">
         <f ca="1">+MOD(Q9+R9,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="1">
         <f ca="1">+MOD(S9+T9,2)</f>
@@ -5639,7 +6355,7 @@
       </c>
       <c r="T17" s="1">
         <f ca="1">+MOD(W9+X9,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" s="1">
         <f ca="1">+MOD(Y9+Z9,2)</f>
@@ -5682,9 +6398,9 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
@@ -5716,11 +6432,11 @@
       <c r="C19" s="13"/>
       <c r="D19" s="1">
         <f ca="1">+MOD(D17+E17,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1">
         <f ca="1">+MOD(F17+G17,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
         <f ca="1">+MOD(H17+I17,2)</f>
@@ -5736,11 +6452,11 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N19" s="14"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" s="13"/>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="1">
@@ -5749,7 +6465,7 @@
       </c>
       <c r="R19" s="1">
         <f ca="1">+IF(AND(NOT(S17),T17),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" s="1">
         <f ca="1">+IF(AND(NOT(U17),V17),1,0)</f>
@@ -5790,9 +6506,9 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
@@ -5827,26 +6543,26 @@
         <v>1</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" ref="E21:G21" ca="1" si="5">+ROUND(RAND(),0)</f>
+        <f t="shared" ref="E21:G21" ca="1" si="6">+ROUND(RAND(),0)</f>
         <v>1</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
       <c r="G21" s="3">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14" t="s">
+      <c r="L21" s="13"/>
+      <c r="M21" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N21" s="14"/>
+      <c r="N21" s="13"/>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="3">
@@ -5855,11 +6571,11 @@
       </c>
       <c r="R21" s="3">
         <f ca="1">+IF(AND(R19=1,E19=1),MOD(1+E21,2),E21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="3">
         <f ca="1">+IF(AND(S19=1,F19=1),MOD(1+F21,2),F21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="3">
         <f ca="1">+IF(AND(T19=1,G19=1),MOD(1+G21,2),G21)</f>
@@ -5909,9 +6625,9 @@
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
@@ -5943,19 +6659,19 @@
       <c r="C23" s="13"/>
       <c r="D23" s="1">
         <f ca="1">+MOD(1+D21+D17,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
         <f ca="1">+MOD(1+E21+F17,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1">
         <f ca="1">+MOD(1+F21+H17,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
         <f ca="1">+MOD(1+G21+J17,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>18</v>
@@ -5963,11 +6679,11 @@
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14" t="s">
+      <c r="L23" s="13"/>
+      <c r="M23" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="14"/>
+      <c r="N23" s="13"/>
       <c r="O23" s="1">
         <f ca="1">+MOD(O17+SUMPRODUCT(Q21:T21,Q23:T23),2)</f>
         <v>1</v>
@@ -5975,11 +6691,11 @@
       <c r="P23" s="13"/>
       <c r="Q23" s="1">
         <f ca="1">+MOD(Q17+R17,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="1">
         <f ca="1">+MOD(S17+T17,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="1">
         <f ca="1">+MOD(U17+V17,2)</f>
@@ -6020,9 +6736,9 @@
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
@@ -6068,16 +6784,16 @@
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N25" s="14"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N25" s="13"/>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="1">
         <f ca="1">+IF(AND(NOT(Q23),R23),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="1">
         <f ca="1">+IF(AND(NOT(S23),T23),1,0)</f>
@@ -6116,9 +6832,9 @@
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
@@ -6153,8 +6869,8 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" ref="E27" ca="1" si="6">+ROUND(RAND(),0)</f>
-        <v>0</v>
+        <f t="shared" ref="E27" ca="1" si="7">+ROUND(RAND(),0)</f>
+        <v>1</v>
       </c>
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
@@ -6162,11 +6878,11 @@
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14" t="s">
+      <c r="L27" s="13"/>
+      <c r="M27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N27" s="14"/>
+      <c r="N27" s="13"/>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
       <c r="Q27" s="3">
@@ -6175,7 +6891,7 @@
       </c>
       <c r="R27" s="3">
         <f ca="1">+IF(AND(R25=1,E25=1),MOD(1+E27,2),E27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="13"/>
       <c r="T27" s="13"/>
@@ -6215,9 +6931,9 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
       <c r="O28" s="13"/>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
@@ -6249,7 +6965,7 @@
       <c r="C29" s="13"/>
       <c r="D29" s="1">
         <f ca="1">+MOD(1+D27+D23,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1">
         <f ca="1">+MOD(1+E27+F23,2)</f>
@@ -6263,11 +6979,11 @@
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14" t="s">
+      <c r="L29" s="13"/>
+      <c r="M29" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="14"/>
+      <c r="N29" s="13"/>
       <c r="O29" s="1">
         <f ca="1">+MOD(O23+SUMPRODUCT(Q27:T27,Q29:T29),2)</f>
         <v>1</v>
@@ -6314,9 +7030,9 @@
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
       <c r="O30" s="13"/>
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
@@ -6348,7 +7064,7 @@
       <c r="C31" s="13"/>
       <c r="D31" s="1">
         <f ca="1">+MOD(D29+E29,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>11</v>
@@ -6359,11 +7075,11 @@
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N31" s="14"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N31" s="13"/>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
       <c r="Q31" s="1">
@@ -6404,9 +7120,9 @@
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
       <c r="K32" s="13"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -6438,7 +7154,7 @@
       <c r="C33" s="13"/>
       <c r="D33" s="3">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
@@ -6447,16 +7163,16 @@
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14" t="s">
+      <c r="L33" s="13"/>
+      <c r="M33" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N33" s="14"/>
+      <c r="N33" s="13"/>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="3">
         <f ca="1">+IF(AND(Q31=1,D31=1),MOD(1+D33,2),D33)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="13"/>
       <c r="S33" s="13"/>
@@ -6493,9 +7209,9 @@
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
       <c r="O34" s="13"/>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
@@ -6538,14 +7254,14 @@
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14" t="s">
+      <c r="L35" s="13"/>
+      <c r="M35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="14"/>
+      <c r="N35" s="13"/>
       <c r="O35" s="1">
         <f ca="1">+MOD(O29+SUMPRODUCT(Q33:T33,Q35:T35),2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="1">
@@ -6586,9 +7302,9 @@
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
       <c r="O36" s="13"/>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
@@ -6629,14 +7345,14 @@
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14" t="s">
+      <c r="L37" s="13"/>
+      <c r="M37" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N37" s="14"/>
+      <c r="N37" s="13"/>
       <c r="O37" s="4">
         <f ca="1">+O35</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
@@ -6672,9 +7388,9 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="13"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
@@ -6710,7 +7426,7 @@
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
-      <c r="L39" s="14"/>
+      <c r="L39" s="13"/>
       <c r="M39" s="10" t="s">
         <v>17</v>
       </c>
@@ -6753,7 +7469,7 @@
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
       <c r="K40" s="13"/>
-      <c r="L40" s="14"/>
+      <c r="L40" s="13"/>
       <c r="M40" s="13"/>
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
@@ -6822,7 +7538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B2B750-DE03-45E3-95DB-CA56FAF0931C}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AD27"/>
@@ -6844,8 +7560,8 @@
         <v>1</v>
       </c>
       <c r="E2" s="6">
-        <f t="shared" ref="E2:K2" ca="1" si="0">+ROUND(RAND(),0)</f>
-        <v>0</v>
+        <f t="shared" ref="E2:G2" ca="1" si="0">+ROUND(RAND(),0)</f>
+        <v>1</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" ca="1" si="0"/>
@@ -6859,22 +7575,22 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
-      <c r="Q2" s="15">
-        <v>0</v>
-      </c>
-      <c r="R2" s="15">
-        <v>1</v>
-      </c>
-      <c r="S2" s="15">
+      <c r="Q2" s="14">
+        <v>0</v>
+      </c>
+      <c r="R2" s="14">
+        <v>1</v>
+      </c>
+      <c r="S2" s="14">
         <v>2</v>
       </c>
-      <c r="T2" s="15">
+      <c r="T2" s="14">
         <v>3</v>
       </c>
       <c r="U2" s="13"/>
@@ -6890,7 +7606,7 @@
       <c r="C3" s="13"/>
       <c r="D3" s="8">
         <f ca="1">+RANDBETWEEN(0,3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
@@ -6920,7 +7636,7 @@
       <c r="C4" s="13"/>
       <c r="D4" s="4">
         <f ca="1">+OFFSET(D2,0,D3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -6942,26 +7658,16 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
     </row>
-    <row r="5" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-    </row>
+    <row r="5" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="14"/>
-    </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-    </row>
+    </row>
+    <row r="7" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
         <v>0</v>
@@ -6972,7 +7678,7 @@
       </c>
       <c r="E8" s="1">
         <f t="shared" ref="E8:G8" ca="1" si="1">+E2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="1"/>
@@ -6985,22 +7691,20 @@
       <c r="H8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="14"/>
       <c r="O8" s="9">
         <f ca="1">+D22</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="1">
         <f ca="1">+IF(Q2=$D3,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" ref="R8:T8" ca="1" si="2">+IF(R2=$D3,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" ca="1" si="2"/>
@@ -7014,18 +7718,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-    </row>
+    <row r="9" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1">
         <f ca="1">+MOD(D8+E8,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <f ca="1">+MOD(F8+G8,2)</f>
@@ -7034,14 +7734,12 @@
       <c r="F10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="14"/>
+      <c r="M10" s="13" t="s">
+        <v>1</v>
+      </c>
       <c r="Q10" s="1">
         <f ca="1">+IF(AND(NOT(Q8),R8),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="1">
         <f ca="1">+IF(AND(NOT(S8),T8),1,0)</f>
@@ -7051,65 +7749,53 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-    </row>
+    <row r="11" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="3">
         <f ca="1">+ROUND(RAND(),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" ref="E12" ca="1" si="3">+ROUND(RAND(),0)</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="14"/>
       <c r="Q12" s="3">
         <f ca="1">+IF(AND(Q10=1,D10=1),MOD(1+D12,2),D12)</f>
         <v>1</v>
       </c>
       <c r="R12" s="3">
         <f ca="1">+IF(AND(R10=1,E10=1),MOD(1+E12,2),E12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-    </row>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1">
         <f ca="1">+MOD(D12+D8,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <f ca="1">+MOD(E12+F8,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="14"/>
       <c r="O14" s="1">
         <f ca="1">+MOD(O8+SUMPRODUCT(Q12:T12,Q14:T14),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="1">
         <f ca="1">+MOD(Q8+R8,2)</f>
@@ -7123,11 +7809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-    </row>
+    <row r="15" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>1</v>
@@ -7139,11 +7821,9 @@
       <c r="E16" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" s="14"/>
+      <c r="M16" s="13" t="s">
+        <v>1</v>
+      </c>
       <c r="Q16" s="1">
         <f ca="1">+IF(AND(NOT(Q14),R14),1,0)</f>
         <v>0</v>
@@ -7152,11 +7832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-    </row>
+    <row r="17" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>2</v>
@@ -7165,40 +7841,32 @@
         <f ca="1">+ROUND(RAND(),0)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14" t="s">
+      <c r="M18" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N18" s="14"/>
       <c r="Q18" s="3">
         <f ca="1">+IF(AND(Q16=1,D16=1),MOD(1+D18,2),D18)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-    </row>
+    <row r="19" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1">
         <f ca="1">+MOD(D18+D14,2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14" t="s">
+      <c r="M20" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="14"/>
       <c r="O20" s="1">
         <f ca="1">+MOD(O14+SUMPRODUCT(Q18:T18,Q20:T20),2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="1">
         <f ca="1">+MOD(Q14+R14,2)</f>
@@ -7208,36 +7876,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:18" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-    </row>
+    <row r="21" spans="2:18" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:18" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="2">
         <f ca="1">+D20</f>
-        <v>1</v>
-      </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N22" s="14"/>
       <c r="O22" s="4">
         <f ca="1">+O20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-    </row>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="2:18" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L24" s="14"/>
       <c r="M24" s="10" t="s">
         <v>17</v>
       </c>
@@ -7247,9 +7904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="L25" s="14"/>
-    </row>
+    <row r="25" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:18" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -7258,7 +7913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
@@ -7269,21 +7924,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"Blank workbook (1)","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"Blank workbook (1)","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D935B92B-7CB7-4F33-8A9E-9593CFA73A38}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F80FD2-C12F-42D4-B161-EC42684C5897}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F80FD2-C12F-42D4-B161-EC42684C5897}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D935B92B-7CB7-4F33-8A9E-9593CFA73A38}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>